--- a/LearningNote/天才交易记录.xlsx
+++ b/LearningNote/天才交易记录.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6121E0C4-1686-4D6B-9F2A-A124D914F50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F7E612-C66F-46CE-863A-3F0AE4AA8D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="交易记录" sheetId="1" r:id="rId1"/>
-    <sheet name="交易统计" sheetId="2" r:id="rId2"/>
-    <sheet name="2026年月度收益" sheetId="3" r:id="rId3"/>
-    <sheet name="压力测试" sheetId="4" r:id="rId4"/>
+    <sheet name="一进二记录" sheetId="5" r:id="rId1"/>
+    <sheet name="交易记录" sheetId="1" r:id="rId2"/>
+    <sheet name="交易统计" sheetId="2" r:id="rId3"/>
+    <sheet name="2026年月度收益" sheetId="3" r:id="rId4"/>
+    <sheet name="压力测试" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="152">
   <si>
     <t>股票代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -950,6 +951,54 @@
   </si>
   <si>
     <t>4.20补了一点仓 23.8，以为低点，还有更低点，还是太着急了，等待企稳后再买入会比较合适。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股票名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否晋级成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝光股份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扬子新材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中晶科技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最后收盘价是否高于开盘价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否已买入</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1027,7 +1076,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1050,6 +1099,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1080,7 +1141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1120,6 +1181,8 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1399,6 +1462,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F121F9D-32D2-4554-970E-AF0242B7D564}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="15.75" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="25.75" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2">
+        <v>600379</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3">
+        <v>2652</v>
+      </c>
+      <c r="C3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4">
+        <v>3026</v>
+      </c>
+      <c r="C4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2266,7 +2429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A58336D1-7469-4FCD-B06B-763F8BB665D8}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2492,7 +2655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A7714E-F2BC-4665-BF6D-241F20928B65}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2950,7 +3113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00AC28AA-D536-48CA-880D-169861BBEC53}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/LearningNote/天才交易记录.xlsx
+++ b/LearningNote/天才交易记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F7E612-C66F-46CE-863A-3F0AE4AA8D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78557C54-8094-4EA7-B34A-D35FF4C8037D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="154">
   <si>
     <t>股票代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -999,6 +999,14 @@
   </si>
   <si>
     <t>是否已买入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1076,7 +1084,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1113,6 +1121,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1141,7 +1155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1183,6 +1197,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1463,7 +1478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F121F9D-32D2-4554-970E-AF0242B7D564}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="15.75" customWidth="1"/>
@@ -1554,6 +1569,18 @@
       <c r="F4" s="17" t="s">
         <v>146</v>
       </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
